--- a/artfynd/A 4532-2025 artfynd.xlsx
+++ b/artfynd/A 4532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3403,6 +3403,426 @@
       <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121062581</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137428335</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>694354</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6659968</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428335</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137428652</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>694362</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6659977</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428652</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137428653</v>
+      </c>
+      <c r="B24" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>694320</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6659966</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428653</t>
         </is>
       </c>
     </row>
@@ -3428,6 +3848,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
